--- a/Arquivos_GNH/dados_acareacoes_GNH.xlsx
+++ b/Arquivos_GNH/dados_acareacoes_GNH.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6052926240357</t>
+          <t>3320070502465</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(GNH INT) PEDRO H R DIAS (SABINOPOLIS)</t>
+          <t>(GNH LOC) CARLOS SOUZA (GUANHAES)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,32 +481,79 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Juliane Miranda Oliveira</t>
+          <t>Edimara Vieira</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5533998570488</t>
+          <t>+5533988322573</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Avenida cristal, Sabinópolis</t>
+          <t>Wantuil caldeira 138 casa, Guanhães</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>calças de tecido feminino*1</t>
+          <t>Nova Sandália Saltinho 5Cm Feminino Babuche Leve e Confortável com Acessórios Personalizados*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-05 17:34:23</t>
+          <t>2026-06-09 10:52:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3320049491137</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(GNH INT) GUSTAVO HENRIQUE (PEÇANHA)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cassia</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+5533998435932</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>rua santo Antônio 32 cada, São Sebastião do Maranhão</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Estojo Triplo Gitroy Nylon 3 Zíper Com super qualidades*1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:52:45</t>
         </is>
       </c>
     </row>

--- a/Arquivos_GNH/dados_acareacoes_GNH.xlsx
+++ b/Arquivos_GNH/dados_acareacoes_GNH.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3320070502465</t>
+          <t>3320009733230</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(GNH LOC) CARLOS SOUZA (GUANHAES)</t>
+          <t>(GNH INT) MADALENA (DOM JOAQUIM)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,39 +481,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Edimara Vieira</t>
+          <t>Sonally Viviane</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5533988322573</t>
+          <t>+5531996529980</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wantuil caldeira 138 casa, Guanhães</t>
+          <t>Rua Sebastião Almeida Costa 56 casa, Dom Joaquim</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nova Sandália Saltinho 5Cm Feminino Babuche Leve e Confortável com Acessórios Personalizados*1</t>
+          <t>Kit 12 Peças 6 Conjunto Roupa Infantil Menina Verão Sortidas Estampadas Camiseta e Shorts Qualidade Excelente Levinhos e Fresquinhos Lindos*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>81.33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-09 10:52:54</t>
+          <t>2026-08-07 11:24:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3320049491137</t>
+          <t>3320004770168</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,32 +528,79 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cassia</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5533998435932</t>
+          <t>+5533998051277</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rua santo Antônio 32 cada, São Sebastião do Maranhão</t>
+          <t>Rua da saudade 101 Casa, São Sebastião do Maranhão</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Estojo Triplo Gitroy Nylon 3 Zíper Com super qualidades*1</t>
+          <t>Mini Shorts Feminino Cintura Baixa Fashion Courino Premium Moda Blogueira Trend 2026*1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>56.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-09 10:52:45</t>
+          <t>2026-08-07 11:23:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3320039745491</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(GNH INT) PATRICK DE PAULA (CMD)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shirlei Rodrigues</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+5531999861673</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Farmacêutico Orlando Guerra 60 Loja, Conceição do Mato Dentro</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fronha Infantil Capa De Travesseiro Patrulha Canina*1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:18:07</t>
         </is>
       </c>
     </row>
